--- a/branches/examples-coherent-case/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/examples-coherent-case/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T10:35:54+00:00</t>
+    <t>2026-10-09T10:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/examples-coherent-case/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/examples-coherent-case/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T10:47:56+00:00</t>
+    <t>2026-10-09T10:56:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
